--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -532,7 +544,7 @@
         <v>64.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03060237178654872</v>
+        <v>0.03060237178654871</v>
       </c>
       <c r="J3" t="n">
         <v>75300</v>
@@ -569,7 +581,7 @@
         <v>28.9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4264313369285802</v>
+        <v>0.4264313369285799</v>
       </c>
       <c r="J4" t="n">
         <v>4774</v>
@@ -730,7 +742,7 @@
         <v>90.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04704275749830538</v>
+        <v>0.04704275749830537</v>
       </c>
       <c r="J9" t="n">
         <v>123804</v>
@@ -767,7 +779,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.484788327891376</v>
+        <v>0.4847883278913757</v>
       </c>
       <c r="J10" t="n">
         <v>90098</v>
@@ -810,85 +822,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>0.68</v>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.39</v>
-      </c>
+        <v>1.01</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0008554030642235538</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>90588</v>
+        <v>822</v>
       </c>
       <c r="K12" t="n">
-        <v>9992</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
         <v>0.68</v>
       </c>
       <c r="D13" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="F13" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="G13" t="n">
-        <v>3.48</v>
+        <v>1.39</v>
       </c>
       <c r="H13" t="n">
-        <v>85.2</v>
+        <v>71.7</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05774539381341278</v>
+        <v>0.0008554030642235527</v>
       </c>
       <c r="J13" t="n">
-        <v>86259</v>
+        <v>90588</v>
       </c>
       <c r="K13" t="n">
-        <v>3929</v>
+        <v>9992</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>0.68</v>
@@ -897,19 +903,25 @@
         <v>0.44</v>
       </c>
       <c r="E14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+        <v>1.06</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.48</v>
+      </c>
       <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05774539381341274</v>
+      </c>
       <c r="J14" t="n">
-        <v>822</v>
+        <v>86259</v>
       </c>
       <c r="K14" t="n">
-        <v>424</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="15">
@@ -940,7 +952,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03399129075024581</v>
+        <v>0.0339912907502458</v>
       </c>
       <c r="J15" t="n">
         <v>4521</v>
@@ -952,7 +964,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -965,7 +977,7 @@
         <v>0.57</v>
       </c>
       <c r="E16" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -974,16 +986,16 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>443</v>
+        <v>81590</v>
       </c>
       <c r="K16" t="n">
-        <v>145</v>
+        <v>8142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>non-alcoholic_fermented_foods</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -996,7 +1008,7 @@
         <v>0.57</v>
       </c>
       <c r="E17" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1005,10 +1017,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>81590</v>
+        <v>443</v>
       </c>
       <c r="K17" t="n">
-        <v>8142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
@@ -1070,7 +1082,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006574139593746981</v>
+        <v>0.006574139593746978</v>
       </c>
       <c r="J19" t="n">
         <v>74040</v>
@@ -1107,7 +1119,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.50137706850404</v>
+        <v>0.5013770685040403</v>
       </c>
       <c r="J20" t="n">
         <v>36197</v>
@@ -1144,7 +1156,7 @@
         <v>56.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2345235869669558</v>
+        <v>0.2345235869669559</v>
       </c>
       <c r="J21" t="n">
         <v>34075</v>
@@ -1212,7 +1224,7 @@
         <v>89.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4263170110816271</v>
+        <v>0.426317011081627</v>
       </c>
       <c r="J23" t="n">
         <v>110943</v>
@@ -1249,7 +1261,7 @@
         <v>82.3</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6203312420698301</v>
+        <v>0.62033124206983</v>
       </c>
       <c r="J24" t="n">
         <v>23709</v>
@@ -1558,7 +1570,7 @@
         <v>98.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7984491065727578</v>
+        <v>0.7984491065727577</v>
       </c>
       <c r="J33" t="n">
         <v>433021</v>
@@ -1595,7 +1607,7 @@
         <v>46.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7146765353733535</v>
+        <v>0.7146765353733536</v>
       </c>
       <c r="J34" t="n">
         <v>41569</v>
@@ -1669,7 +1681,7 @@
         <v>90.5</v>
       </c>
       <c r="I36" t="n">
-        <v>0.02912942499259846</v>
+        <v>0.02912942499259806</v>
       </c>
       <c r="J36" t="n">
         <v>750</v>

--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -1,40 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t>Exposure</t>
+  </si>
+  <si>
+    <t>number studies</t>
+  </si>
+  <si>
+    <t>Pooled RR</t>
+  </si>
+  <si>
+    <t>lower CI RR</t>
+  </si>
+  <si>
+    <t>upper CI RR</t>
+  </si>
+  <si>
+    <t>lower PI RR</t>
+  </si>
+  <si>
+    <t>upper PI RR</t>
+  </si>
+  <si>
+    <t>I^2 (%)</t>
+  </si>
+  <si>
+    <t>eggers p-value</t>
+  </si>
+  <si>
+    <t>total N</t>
+  </si>
+  <si>
+    <t>total Cases</t>
+  </si>
+  <si>
+    <t>eggs</t>
+  </si>
+  <si>
+    <t>folic_acid</t>
+  </si>
+  <si>
+    <t>lutein</t>
+  </si>
+  <si>
+    <t>antioxidants</t>
+  </si>
+  <si>
+    <t>mineral_supplements</t>
+  </si>
+  <si>
+    <t>legumes</t>
+  </si>
+  <si>
+    <t>vitamin_e</t>
+  </si>
+  <si>
+    <t>vitamin_c</t>
+  </si>
+  <si>
+    <t>mediterranean_diet</t>
+  </si>
+  <si>
+    <t>garlic</t>
+  </si>
+  <si>
+    <t>quercetin</t>
+  </si>
+  <si>
+    <t>calcium</t>
+  </si>
+  <si>
+    <t>beta-carotene</t>
+  </si>
+  <si>
+    <t>lycopene</t>
+  </si>
+  <si>
+    <t>fermented_foods</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>yogurt</t>
+  </si>
+  <si>
+    <t>vitamin_d</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>green_tea</t>
+  </si>
+  <si>
+    <t>vitamin_b12</t>
+  </si>
+  <si>
+    <t>fish_oil</t>
+  </si>
+  <si>
+    <t>copper</t>
+  </si>
+  <si>
+    <t>vitamin_a</t>
+  </si>
+  <si>
+    <t>caffeine</t>
+  </si>
+  <si>
+    <t>carnitine</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>selenium</t>
+  </si>
+  <si>
+    <t>phosphorus</t>
+  </si>
+  <si>
+    <t>omega-3_fatty_acids</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
+    <t>zinc</t>
+  </si>
+  <si>
+    <t>red_meat</t>
+  </si>
+  <si>
+    <t>iron</t>
+  </si>
+  <si>
+    <t>lactobacillus</t>
+  </si>
+  <si>
+    <t>dehydroepiandrosterone</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +194,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,1308 +511,1162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>number studies</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Pooled RR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>lower CI RR</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>upper CI RR</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>lower PI RR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>upper PI RR</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>I^2 (%)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>eggers p-value</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total N</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>total Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>0.27</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.36</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.93</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>541</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>161</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.31</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.16</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.57</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.02</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>3.94</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>64.2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.03060237178654872</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="I3">
+        <v>0.03060237178654871</v>
+      </c>
+      <c r="J3">
         <v>75300</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>667</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.51</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.64</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.28</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.9</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>28.9</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.4264313369285802</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I4">
+        <v>0.4264313369285799</v>
+      </c>
+      <c r="J4">
         <v>4774</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>1547</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>antioxidants</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.53</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.29</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.98</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>41.5</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1150</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>564</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mineral_supplements</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.53</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.33</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.91</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>3596</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>709</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>legumes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.58</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.42</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.79</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>1591</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>523</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.59</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.46</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.75</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>23</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>1592</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>711</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.61</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.34</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1.09</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>5.28</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>90.7</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.04704275749830538</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I9">
+        <v>0.04704275749830537</v>
+      </c>
+      <c r="J9">
         <v>123804</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>13929</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mediterranean_diet</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0.63</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.37</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1.08</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>509.19</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>93.09999999999999</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.484788327891376</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I10">
+        <v>0.4847883278913757</v>
+      </c>
+      <c r="J10">
         <v>90098</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>3100</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>garlic</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>0.65</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.45</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.93</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>1362</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>454</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>0.68</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.44</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>1.01</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>822</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>424</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
         <v>7</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.68</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.53</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.86</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.33</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1.39</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>71.7</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.0008554030642235538</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="I13">
+        <v>0.0008554030642235527</v>
+      </c>
+      <c r="J13">
         <v>90588</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9992</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>beta-carotene</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>0.68</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.44</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1.06</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.13</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>3.48</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>85.2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.05774539381341278</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14">
+        <v>0.05774539381341274</v>
+      </c>
+      <c r="J14">
         <v>86259</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>3929</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.73</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.49</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1.08</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.14</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>3.72</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>70.59999999999999</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.03399129075024581</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I15">
+        <v>0.0339912907502458</v>
+      </c>
+      <c r="J15">
         <v>4521</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>1592</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>fermented_foods</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.77</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.57</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>1.04</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="J16">
         <v>81590</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>8142</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>olive</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>0.77</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.57</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1.25</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>443</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>145</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>0.77</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.57</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>1.04</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <v>81590</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>8142</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
         <v>9</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.78</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.63</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.97</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.42</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>1.45</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>64.09999999999999</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.006574139593746981</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="I19">
+        <v>0.006574139593746978</v>
+      </c>
+      <c r="J19">
         <v>74040</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>3664</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
         <v>6</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.78</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.59</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>1.04</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.32</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>1.91</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>72.90000000000001</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.50137706850404</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="I20">
+        <v>0.5013770685040403</v>
+      </c>
+      <c r="J20">
         <v>36197</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>2521</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>0.79</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.62</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>1.01</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.31</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>2.01</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>56.7</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.2345235869669558</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I21">
+        <v>0.2345235869669559</v>
+      </c>
+      <c r="J21">
         <v>34075</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>1876</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vitamin_b12</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>0.83</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.74</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.93</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <v>12437</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>386</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>fish_oil</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
         <v>3</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>0.87</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.48</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>1.61</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>1689.46</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>89.5</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.4263170110816271</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I23">
+        <v>0.426317011081627</v>
+      </c>
+      <c r="J23">
         <v>110943</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>2072</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>0.87</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.34</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>2.22</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.01</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>52.9</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>82.3</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.6203312420698301</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I24">
+        <v>0.62033124206983</v>
+      </c>
+      <c r="J24">
         <v>23709</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>1361</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
         <v>5</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.91</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.71</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>1.17</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.4</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>2.07</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>71.40000000000001</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>0.8780871428365096</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>26530</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>7689</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>caffeine</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>0.91</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.74</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>1.11</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.4</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>2.07</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>60.8</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>0.8631142054417383</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>150854</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>1222</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>carnitine</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>0.92</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.83</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>1706</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>853</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D28">
+        <v>0.71</v>
+      </c>
+      <c r="E28">
+        <v>1.24</v>
+      </c>
+      <c r="F28">
+        <v>0.37</v>
+      </c>
+      <c r="G28">
+        <v>2.37</v>
+      </c>
+      <c r="H28">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0.8979661633637739</v>
+      </c>
+      <c r="J28">
+        <v>431748</v>
+      </c>
+      <c r="K28">
+        <v>26221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29">
         <v>1</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C29">
         <v>0.99</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D29">
         <v>0.88</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E29">
         <v>1.12</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>121885</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K29">
         <v>12906</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>phosphorus</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
         <v>1</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C30">
         <v>1</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D30">
         <v>1</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E30">
         <v>1</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>12437</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30">
         <v>386</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>omega-3_fatty_acids</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
         <v>7</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C31">
         <v>1.13</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D31">
         <v>0.66</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31">
         <v>1.91</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F31">
         <v>0.17</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G31">
         <v>7.68</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H31">
         <v>97.8</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I31">
         <v>0.7232591647058118</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31">
         <v>471078</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K31">
         <v>7212</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>soy</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
         <v>9</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C32">
         <v>1.18</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D32">
         <v>0.76</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E32">
         <v>1.83</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F32">
         <v>0.23</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G32">
         <v>6.08</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32">
         <v>97.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32">
         <v>0.9295959990787233</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32">
         <v>151854</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32">
         <v>3291</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
         <v>2</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C33">
         <v>1.21</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D33">
         <v>0.99</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33">
         <v>1.48</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="J33">
         <v>61032</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33">
         <v>788</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>7</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G33" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="H33" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.7984491065727578</v>
-      </c>
-      <c r="J33" t="n">
-        <v>433021</v>
-      </c>
-      <c r="K33" t="n">
-        <v>26434</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
         <v>3</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>1.4</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>1.17</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>1.66</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>0.25</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>7.81</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>46.2</v>
       </c>
-      <c r="I34" t="n">
-        <v>0.7146765353733535</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I34">
+        <v>0.7146765353733536</v>
+      </c>
+      <c r="J34">
         <v>41569</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>1404</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>iron</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>1.47</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>1.28</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>1.69</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>1.08</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>2.01</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
         <v>0.5692336538290566</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>72387</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>2803</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>lactobacillus</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36">
         <v>3</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>1.59</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>0.45</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>5.63</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
         <v>11519830.38</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>90.5</v>
       </c>
-      <c r="I36" t="n">
-        <v>0.02912942499259846</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="I36">
+        <v>0.02912942499259806</v>
+      </c>
+      <c r="J36">
         <v>750</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>510</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dehydroepiandrosterone</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>1.67</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>1.05</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>2.51</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="J37">
         <v>667</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>313</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,7 +1026,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1057,7 +1057,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1230,224 +1230,230 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
         <v>0.83</v>
       </c>
       <c r="D24" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="E24" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.46</v>
+      </c>
       <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>60.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.02006627521428399</v>
+      </c>
       <c r="J24" t="n">
-        <v>12437</v>
+        <v>73656</v>
       </c>
       <c r="K24" t="n">
-        <v>386</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>0.83</v>
       </c>
       <c r="D25" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="E25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.46</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.02006627521428399</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>73656</v>
+        <v>12437</v>
       </c>
       <c r="K25" t="n">
-        <v>3536</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C26" t="n">
         <v>0.91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="G26" t="n">
-        <v>2.07</v>
+        <v>1.46</v>
       </c>
       <c r="H26" t="n">
-        <v>60.8</v>
+        <v>83.7</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8631142054417383</v>
+        <v>0.4730156973814423</v>
       </c>
       <c r="J26" t="n">
-        <v>150854</v>
+        <v>2962063</v>
       </c>
       <c r="K26" t="n">
-        <v>1222</v>
+        <v>189136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D27" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+        <v>1.11</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.07</v>
+      </c>
       <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>60.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8631142054417383</v>
+      </c>
       <c r="J27" t="n">
-        <v>1706</v>
+        <v>150854</v>
       </c>
       <c r="K27" t="n">
-        <v>853</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D28" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="E28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.8979661633637739</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>431748</v>
+        <v>1706</v>
       </c>
       <c r="K28" t="n">
-        <v>26221</v>
+        <v>853</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="E29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+        <v>1.24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.37</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8979661633637739</v>
+      </c>
       <c r="J29" t="n">
-        <v>121885</v>
+        <v>431748</v>
       </c>
       <c r="K29" t="n">
-        <v>12906</v>
+        <v>26221</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1456,208 +1462,208 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>12437</v>
+        <v>121885</v>
       </c>
       <c r="K30" t="n">
-        <v>386</v>
+        <v>12906</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7.68</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.7232591647058118</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>471078</v>
+        <v>12437</v>
       </c>
       <c r="K31" t="n">
-        <v>7212</v>
+        <v>386</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="D32" t="n">
-        <v>1.17</v>
+        <v>0.66</v>
       </c>
       <c r="E32" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="F32" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="G32" t="n">
-        <v>7.81</v>
+        <v>7.68</v>
       </c>
       <c r="H32" t="n">
-        <v>46.2</v>
+        <v>97.8</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7146765353733536</v>
+        <v>0.7232591647058118</v>
       </c>
       <c r="J32" t="n">
-        <v>41569</v>
+        <v>471078</v>
       </c>
       <c r="K32" t="n">
-        <v>1404</v>
+        <v>7212</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="D33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="E33" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="F33" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="G33" t="n">
-        <v>6.72</v>
+        <v>7.81</v>
       </c>
       <c r="H33" t="n">
-        <v>21.1</v>
+        <v>46.2</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7203820715741027</v>
+        <v>0.7146765353733536</v>
       </c>
       <c r="J33" t="n">
-        <v>66907</v>
+        <v>41569</v>
       </c>
       <c r="K33" t="n">
-        <v>2633</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lactobacillus</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="D34" t="n">
-        <v>0.45</v>
+        <v>1.23</v>
       </c>
       <c r="E34" t="n">
-        <v>5.63</v>
+        <v>1.77</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="G34" t="n">
-        <v>11519830.38</v>
+        <v>6.72</v>
       </c>
       <c r="H34" t="n">
-        <v>90.5</v>
+        <v>21.1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02912942499259806</v>
+        <v>0.7203820715741027</v>
       </c>
       <c r="J34" t="n">
-        <v>750</v>
+        <v>66907</v>
       </c>
       <c r="K34" t="n">
-        <v>510</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>lactobacillus</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="D35" t="n">
-        <v>1.05</v>
+        <v>0.45</v>
       </c>
       <c r="E35" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+        <v>5.63</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11519830.38</v>
+      </c>
       <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.02912942499259806</v>
+      </c>
       <c r="J35" t="n">
-        <v>667</v>
+        <v>750</v>
       </c>
       <c r="K35" t="n">
-        <v>313</v>
+        <v>510</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>2.24</v>
+        <v>1.67</v>
       </c>
       <c r="D36" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="E36" t="n">
-        <v>3.56</v>
+        <v>2.51</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1666,9 +1672,40 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
+        <v>667</v>
+      </c>
+      <c r="K36" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
         <v>12437</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>386</v>
       </c>
     </row>

--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -526,156 +526,162 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
+        <v>0.73</v>
+      </c>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
       <c r="H2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="n"/>
       <c r="J2" s="8" t="n">
-        <v>541</v>
+        <v>74680</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>161</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="n"/>
       <c r="J3" s="8" t="n">
-        <v>1082</v>
+        <v>843</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>541</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
+        <v>0.71</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>26.86</v>
+      </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7" t="inlineStr"/>
+        <v>62.8</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.2282168407301836</v>
+      </c>
       <c r="J4" s="8" t="n">
-        <v>74680</v>
+        <v>3315</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>412</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>mineral_supplements</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n">
-        <v>843</v>
+        <v>3596</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>332</v>
+        <v>709</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>26.86</v>
+        <v>5.64</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>62.8</v>
+        <v>24.9</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.2282168407301835</v>
+        <v>0.1753492059479154</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>3315</v>
@@ -687,675 +693,687 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>mineral_supplements</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>509.19</v>
+      </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr"/>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.484788327891376</v>
+      </c>
       <c r="J7" s="8" t="n">
-        <v>3596</v>
+        <v>90098</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>709</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>5.64</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="6" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.1753492059479153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n"/>
       <c r="J8" s="8" t="n">
-        <v>3315</v>
+        <v>812</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>1227</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>garlic</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>509.19</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="6" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0.4847883278913757</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n"/>
       <c r="J9" s="8" t="n">
-        <v>90098</v>
+        <v>1362</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>3100</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>garlic</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.084037740305833</v>
+      </c>
       <c r="J10" s="8" t="n">
-        <v>1362</v>
+        <v>6240</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>454</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
+        <v>1.24</v>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="7" t="inlineStr"/>
+        <v>86.2</v>
+      </c>
+      <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="n">
-        <v>1089</v>
+        <v>30376</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>556</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>green_tea</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.43</v>
+        <v>0.03</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.09</v>
+        <v>16.43</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.6</v>
+        <v>46.3</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.084037740305833</v>
+        <v>0.3550326464827145</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>6240</v>
+        <v>3331</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1445</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>127.74</v>
+      </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7" t="inlineStr"/>
+        <v>84.2</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0290298668942214</v>
+      </c>
       <c r="J14" s="8" t="n">
-        <v>822</v>
+        <v>95991</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>424</v>
+        <v>933</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>green_tea</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.96</v>
+        <v>1.21</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>16.43</v>
+        <v>5.72</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>46.3</v>
+        <v>78.7</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.3550326464827144</v>
+        <v>0.8535116576994071</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>3331</v>
+        <v>4413</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>1564</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.37</v>
+        <v>0.57</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="n"/>
       <c r="J16" s="8" t="n">
-        <v>49964</v>
+        <v>443</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>444</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>5.72</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>78.7</v>
+        <v>75</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.8535116576994072</v>
+        <v>0.1542885202153812</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>4413</v>
+        <v>66026</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2105</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
+        <v>0.93</v>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
       <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="n"/>
       <c r="J18" s="8" t="n">
-        <v>443</v>
+        <v>12437</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>145</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
+        <v>1.15</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2.43</v>
+      </c>
       <c r="H19" s="6" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="I19" s="7" t="inlineStr"/>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.6898302519232826</v>
+      </c>
       <c r="J19" s="8" t="n">
-        <v>2233</v>
+        <v>457863</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>686</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
+        <v>2.07</v>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="inlineStr"/>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="I20" s="7" t="n"/>
       <c r="J20" s="8" t="n">
-        <v>12437</v>
+        <v>121756</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>386</v>
+        <v>13138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
+        <v>1.61</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1689.46</v>
+      </c>
       <c r="H21" s="6" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I21" s="7" t="inlineStr"/>
+        <v>89.5</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.4263170110816271</v>
+      </c>
       <c r="J21" s="8" t="n">
-        <v>121756</v>
+        <v>110943</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>13138</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>lactobacillus</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>2.43</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
       <c r="H22" s="6" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>0.6898302519232826</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n"/>
       <c r="J22" s="8" t="n">
-        <v>457863</v>
+        <v>73224</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>4240</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>66.7</v>
+        <v>60.8</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.09847070813823804</v>
+        <v>0.8631142054417384</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>66026</v>
+        <v>150854</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>3042</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>2.07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
       <c r="H24" s="6" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0.8631142054417384</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n"/>
       <c r="J24" s="8" t="n">
-        <v>150854</v>
+        <v>1706</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>1222</v>
+        <v>853</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.57</v>
+        <v>0.02</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.46</v>
+        <v>37.32</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>83.7</v>
+        <v>65.2</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.4730156973814422</v>
+        <v>0.4130854811476988</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2962063</v>
+        <v>3463</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>189136</v>
+        <v>987</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
+        <v>1.05</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.4</v>
+      </c>
       <c r="H26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.6977704271423141</v>
+      </c>
       <c r="J26" s="8" t="n">
-        <v>1706</v>
+        <v>3080855</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>853</v>
+        <v>192818</v>
       </c>
     </row>
     <row r="27">
@@ -1376,12 +1394,12 @@
       <c r="E27" s="5" t="n">
         <v>1.12</v>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
       <c r="H27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="n"/>
       <c r="J27" s="8" t="n">
         <v>121885</v>
       </c>
@@ -1407,12 +1425,12 @@
       <c r="E28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n">
         <v>12437</v>
       </c>
@@ -1423,193 +1441,199 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.95</v>
+        <v>0.44</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+        <v>3.21</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>106863.06</v>
+      </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="7" t="inlineStr"/>
+        <v>78.3</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.8203014741020929</v>
+      </c>
       <c r="J29" s="8" t="n">
-        <v>1362</v>
+        <v>14421</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>454</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
+        <v>1.66</v>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="n">
-        <v>39169</v>
+        <v>1362</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>561</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>6.72</v>
-      </c>
+        <v>1.46</v>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
       <c r="H31" s="6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>0.7203820715741027</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="n">
-        <v>66907</v>
+        <v>39169</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>2633</v>
+        <v>561</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.01</v>
+      </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="n">
+        <v>0.5692336538290566</v>
+      </c>
       <c r="J32" s="8" t="n">
-        <v>667</v>
+        <v>72387</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>313</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
+        <v>2.51</v>
+      </c>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
       <c r="H33" s="6" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="I33" s="7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="n"/>
       <c r="J33" s="8" t="n">
-        <v>323215</v>
+        <v>667</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>10020</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1.26</v>
+        <v>0.96</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
+        <v>3.82</v>
+      </c>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
       <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="7" t="inlineStr"/>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="I34" s="7" t="n"/>
       <c r="J34" s="8" t="n">
-        <v>12437</v>
+        <v>323215</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>386</v>
+        <v>10020</v>
       </c>
     </row>
   </sheetData>

--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -613,7 +613,7 @@
         <v>62.8</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.2282168407301836</v>
+        <v>0.2282168407301835</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>3315</v>
@@ -681,7 +681,7 @@
         <v>24.9</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.1753492059479154</v>
+        <v>0.1753492059479153</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>3315</v>
@@ -718,7 +718,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.484788327891376</v>
+        <v>0.4847883278913757</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>90098</v>
@@ -916,7 +916,7 @@
         <v>46.3</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.3550326464827145</v>
+        <v>0.3550326464827144</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>3331</v>
@@ -953,7 +953,7 @@
         <v>84.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0290298668942214</v>
+        <v>0.02902986689422141</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>95991</v>
@@ -990,7 +990,7 @@
         <v>78.7</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.8535116576994071</v>
+        <v>0.8535116576994072</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>4413</v>
@@ -1058,7 +1058,7 @@
         <v>75</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.1542885202153812</v>
+        <v>0.1542885202153811</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>66026</v>
@@ -1330,7 +1330,7 @@
         <v>65.2</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.4130854811476988</v>
+        <v>0.4130854811476984</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>3463</v>
@@ -1367,7 +1367,7 @@
         <v>80</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.6977704271423141</v>
+        <v>0.6977704271423137</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>3080855</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.5692336538290566</v>
+        <v>0.5692336538290563</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>72387</v>

--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -526,17 +526,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0.73</v>
@@ -548,29 +548,29 @@
       </c>
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="8" t="n">
-        <v>74680</v>
+        <v>1082</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>412</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0.49</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
@@ -579,270 +579,264 @@
       </c>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="8" t="n">
-        <v>843</v>
+        <v>74680</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>332</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>26.86</v>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0.2282168407301835</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4" s="7" t="n"/>
       <c r="J4" s="8" t="n">
-        <v>3315</v>
+        <v>843</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>1227</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>mineral_supplements</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
+        <v>0.71</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>26.86</v>
+      </c>
       <c r="H5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7" t="n"/>
+        <v>62.8</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0.2282168407301835</v>
+      </c>
       <c r="J5" s="8" t="n">
-        <v>3596</v>
+        <v>3315</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>709</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>mineral_supplements</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>5.64</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
       <c r="H6" s="6" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.1753492059479153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="n"/>
       <c r="J6" s="8" t="n">
-        <v>3315</v>
+        <v>3596</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1227</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>509.19</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="6" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0.4847883278913757</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" s="8" t="n">
-        <v>90098</v>
+        <v>871</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>3100</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
+        <v>0.78</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5.64</v>
+      </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n"/>
+        <v>24.9</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.1753492059479153</v>
+      </c>
       <c r="J8" s="8" t="n">
-        <v>812</v>
+        <v>3315</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>417</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>garlic</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
+        <v>1.08</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>509.19</v>
+      </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="n"/>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.4847883278913757</v>
+      </c>
       <c r="J9" s="8" t="n">
-        <v>1362</v>
+        <v>90098</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>454</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1.09</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
       <c r="H10" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.084037740305833</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="n"/>
       <c r="J10" s="8" t="n">
-        <v>6240</v>
+        <v>812</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>1445</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>garlic</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
@@ -851,319 +845,325 @@
       </c>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n">
-        <v>822</v>
+        <v>1362</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>424</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>0.68</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+        <v>0.84</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H12" s="6" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="I12" s="7" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.084037740305833</v>
+      </c>
       <c r="J12" s="8" t="n">
-        <v>30376</v>
+        <v>6240</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>2937</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>green_tea</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>16.43</v>
-      </c>
+        <v>1.01</v>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="6" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>0.3550326464827144</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="n">
-        <v>3331</v>
+        <v>822</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1564</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>green_tea</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>127.74</v>
+        <v>16.43</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>84.2</v>
+        <v>46.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.02902986689422141</v>
+        <v>0.3550326464827144</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>95991</v>
+        <v>3331</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>933</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>5.72</v>
+        <v>127.74</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>78.7</v>
+        <v>84.2</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.8535116576994072</v>
+        <v>0.02902986689422141</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>4413</v>
+        <v>95991</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>2105</v>
+        <v>933</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
+        <v>1.21</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.72</v>
+      </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n"/>
+        <v>78.7</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.8535116576994072</v>
+      </c>
       <c r="J16" s="8" t="n">
-        <v>443</v>
+        <v>4413</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>145</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>3.33</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
       <c r="H17" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0.1542885202153811</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="n"/>
       <c r="J17" s="8" t="n">
-        <v>66026</v>
+        <v>443</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2398</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.74</v>
+        <v>0.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+        <v>1.14</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.33</v>
+      </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.1542885202153811</v>
+      </c>
       <c r="J18" s="8" t="n">
-        <v>12437</v>
+        <v>66026</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>386</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>2.43</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="6" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>0.6898302519232826</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="n"/>
       <c r="J19" s="8" t="n">
-        <v>457863</v>
+        <v>12437</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>4240</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>0.86</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
+        <v>1.15</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.43</v>
+      </c>
       <c r="H20" s="6" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I20" s="7" t="n"/>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.6898302519232826</v>
+      </c>
       <c r="J20" s="8" t="n">
-        <v>121756</v>
+        <v>457863</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>13138</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="21">
@@ -1206,224 +1206,230 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>lactobacillus</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
+        <v>1.11</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2.07</v>
+      </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n"/>
+        <v>60.8</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.8631142054417384</v>
+      </c>
       <c r="J22" s="8" t="n">
-        <v>73224</v>
+        <v>150854</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>2270</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>2.07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="6" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>0.8631142054417384</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="n"/>
       <c r="J23" s="8" t="n">
-        <v>150854</v>
+        <v>1706</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>1222</v>
+        <v>853</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>0.92</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
+        <v>1.29</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>37.32</v>
+      </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="n"/>
+        <v>65.2</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.4130854811476984</v>
+      </c>
       <c r="J24" s="8" t="n">
-        <v>1706</v>
+        <v>3463</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>853</v>
+        <v>987</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="D25" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>0.66</v>
       </c>
-      <c r="E25" s="5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0.02</v>
-      </c>
       <c r="G25" s="5" t="n">
-        <v>37.32</v>
+        <v>1.4</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>65.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.4130854811476984</v>
+        <v>0.7559650135603323</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>3463</v>
+        <v>411289</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>987</v>
+        <v>8229</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>1.4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>0.6977704271423137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I26" s="7" t="n"/>
       <c r="J26" s="8" t="n">
-        <v>3080855</v>
+        <v>12437</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>192818</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.99</v>
+        <v>1.19</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
+        <v>3.21</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>106863.06</v>
+      </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="7" t="n"/>
+        <v>78.3</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.8203014741020929</v>
+      </c>
       <c r="J27" s="8" t="n">
-        <v>121885</v>
+        <v>14421</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>12906</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1432,66 +1438,60 @@
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n">
-        <v>12437</v>
+        <v>1362</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>386</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>106863.06</v>
-      </c>
+        <v>1.46</v>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
       <c r="H29" s="6" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0.8203014741020929</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="n">
-        <v>14421</v>
+        <v>39169</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>1272</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
@@ -1500,144 +1500,82 @@
       </c>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="n">
-        <v>1362</v>
+        <v>68019</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>454</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
+        <v>1.69</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2.01</v>
+      </c>
       <c r="H31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="7" t="n"/>
+      <c r="I31" s="7" t="n">
+        <v>0.5692336538290563</v>
+      </c>
       <c r="J31" s="8" t="n">
-        <v>39169</v>
+        <v>72387</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>561</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>2.01</v>
-      </c>
+        <v>2.51</v>
+      </c>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="7" t="n">
-        <v>0.5692336538290563</v>
-      </c>
+      <c r="I32" s="7" t="n"/>
       <c r="J32" s="8" t="n">
-        <v>72387</v>
+        <v>667</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>2803</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>dehydroepiandrosterone</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="8" t="n">
-        <v>667</v>
-      </c>
-      <c r="K33" s="8" t="n">
         <v>313</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="6" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="8" t="n">
-        <v>323215</v>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>10020</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -533,13 +533,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
@@ -564,13 +564,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
@@ -595,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -626,25 +626,25 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>26.86</v>
+        <v>32.17</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0.2282168407301835</v>
+        <v>0.2506814459510834</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>3315</v>
@@ -663,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
@@ -694,13 +694,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
@@ -725,25 +725,25 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>5.64</v>
+        <v>6.39</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.1753492059479153</v>
+        <v>0.1836147138174006</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>3315</v>
@@ -762,25 +762,25 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>509.19</v>
+        <v>853.0599999999999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.4847883278913757</v>
+        <v>0.4931648603872096</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>90098</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0.98</v>
@@ -830,13 +830,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
@@ -861,25 +861,25 @@
         <v>4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>1.09</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.084037740305833</v>
+        <v>0.09410146376052672</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>6240</v>
@@ -898,10 +898,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1.01</v>
@@ -929,25 +929,25 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>16.43</v>
+        <v>21.88</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>46.3</v>
+        <v>47.7</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.3550326464827144</v>
+        <v>0.3625177001442668</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>3331</v>
@@ -969,7 +969,7 @@
         <v>0.73</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>1.13</v>
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>127.74</v>
+        <v>147.01</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>84.2</v>
+        <v>84.5</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.02902986689422141</v>
+        <v>0.0282125522798201</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>95991</v>
@@ -1003,25 +1003,25 @@
         <v>4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>1.21</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>5.72</v>
+        <v>6.33</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>78.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.8535116576994072</v>
+        <v>0.8911172970547432</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>4413</v>
@@ -1040,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
@@ -1071,25 +1071,25 @@
         <v>4</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3.33</v>
+        <v>3.63</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.1542885202153811</v>
+        <v>0.1636376558732789</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>66026</v>
@@ -1108,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0.93</v>
@@ -1139,25 +1139,25 @@
         <v>5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.6898302519232826</v>
+        <v>0.6742434715505108</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>457863</v>
@@ -1179,22 +1179,22 @@
         <v>0.87</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1689.46</v>
+        <v>2410.29</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>89.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.4263170110816271</v>
+        <v>0.2543666266957765</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>110943</v>
@@ -1213,25 +1213,25 @@
         <v>4</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>60.8</v>
+        <v>60.6</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.8631142054417384</v>
+        <v>0.8733935157460906</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>150854</v>
@@ -1250,10 +1250,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>1</v>
@@ -1281,25 +1281,25 @@
         <v>3</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>37.32</v>
+        <v>52.81</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>65.2</v>
+        <v>65.7</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.4130854811476984</v>
+        <v>0.3411114014943947</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>3463</v>
@@ -1327,16 +1327,16 @@
         <v>1.08</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>73.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.7559650135603323</v>
+        <v>0.7583025598842165</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>411289</v>
@@ -1386,25 +1386,25 @@
         <v>3</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>106863.06</v>
+        <v>426352.61</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>78.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.8203014741020929</v>
+        <v>0.9620074682802919</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>14421</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1454,13 +1454,13 @@
         <v>2</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
@@ -1516,25 +1516,25 @@
         <v>4</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.5692336538290563</v>
+        <v>0.3723401072937605</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>72387</v>
@@ -1553,13 +1553,13 @@
         <v>1</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2.51</v>
+        <v>3.04</v>
       </c>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>

--- a/Plot/exposures_meta_analysis_uterine_combined.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_combined.xlsx
@@ -780,7 +780,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.4931648603872096</v>
+        <v>0.4931648603872101</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>90098</v>
@@ -879,7 +879,7 @@
         <v>1.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.09410146376052672</v>
+        <v>0.09410146376052661</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>6240</v>
@@ -947,7 +947,7 @@
         <v>47.7</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.3625177001442668</v>
+        <v>0.3625177001442669</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>3331</v>
@@ -1021,7 +1021,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.8911172970547432</v>
+        <v>0.8911172970547433</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>4413</v>
@@ -1064,248 +1064,242 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>3.63</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
       <c r="H18" s="6" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>0.1636376558732789</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="I18" s="7" t="n"/>
       <c r="J18" s="8" t="n">
-        <v>66026</v>
+        <v>2233</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>2398</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
+        <v>1.15</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3.63</v>
+      </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="n"/>
+        <v>75.7</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.1636376558732789</v>
+      </c>
       <c r="J19" s="8" t="n">
-        <v>12437</v>
+        <v>66026</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>386</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>2.54</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="6" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0.6742434715505108</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n"/>
       <c r="J20" s="8" t="n">
-        <v>457863</v>
+        <v>12437</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>4240</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1.64</v>
+        <v>1.16</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2410.29</v>
+        <v>2.54</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>89.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.2543666266957765</v>
+        <v>0.6742434715505108</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>110943</v>
+        <v>457863</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>2072</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>2.09</v>
+        <v>2410.29</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>60.6</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.8733935157460906</v>
+        <v>0.2543666266957765</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>150854</v>
+        <v>110943</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>1222</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
+        <v>1.12</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>2.09</v>
+      </c>
       <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7" t="n"/>
+        <v>60.6</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.8733935157460906</v>
+      </c>
       <c r="J23" s="8" t="n">
-        <v>1706</v>
+        <v>150854</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>853</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>0.91</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>52.81</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
       <c r="H24" s="6" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0.3411114014943947</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n"/>
       <c r="J24" s="8" t="n">
-        <v>3463</v>
+        <v>1706</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>987</v>
+        <v>853</v>
       </c>
     </row>
     <row r="25">
@@ -1379,57 +1373,51 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>426352.61</v>
-      </c>
+        <v>1.79</v>
+      </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
       <c r="H27" s="6" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>0.9620074682802919</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="n"/>
       <c r="J27" s="8" t="n">
-        <v>14421</v>
+        <v>1362</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>1272</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1438,29 +1426,29 @@
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n">
-        <v>1362</v>
+        <v>39169</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>454</v>
+        <v>561</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
@@ -1469,97 +1457,97 @@
       </c>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="n">
-        <v>39169</v>
+        <v>68019</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>561</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
+        <v>1.82</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2.6</v>
+      </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.3723401072937606</v>
+      </c>
       <c r="J30" s="8" t="n">
-        <v>68019</v>
+        <v>72387</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>2109</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>2.6</v>
-      </c>
+        <v>3.04</v>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
       <c r="H31" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>0.3723401072937605</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="n">
-        <v>72387</v>
+        <v>667</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>2803</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3.04</v>
+        <v>4.41</v>
       </c>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
@@ -1568,10 +1556,10 @@
       </c>
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="8" t="n">
-        <v>667</v>
+        <v>13139</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>313</v>
+        <v>791</v>
       </c>
     </row>
   </sheetData>
